--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260716.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260716.xlsx
@@ -645,17 +645,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>67,387,245</t>
+          <t>171,709,245</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -667,17 +667,17 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>171,709,245</t>
+          <t>67,387,245</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
